--- a/Internal1_template.xlsx
+++ b/Internal1_template.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedarshad/Desktop/CO's Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25643227-5470-9B47-867C-A08AD08BA000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526795AB-06E5-E54A-BD74-5CD716545195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{E8323F2F-BE12-A140-9456-E8FB5605DC87}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,43 +38,133 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>ROLL.NO</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>CO 1</t>
-  </si>
-  <si>
-    <t>CO 2</t>
-  </si>
-  <si>
-    <t>CO 3</t>
-  </si>
-  <si>
-    <t>CO 4</t>
-  </si>
-  <si>
-    <t>CO 5</t>
-  </si>
-  <si>
-    <t>CO 6</t>
-  </si>
-  <si>
-    <t>REG.NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNAL 1 </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>Sl. No</t>
+  </si>
+  <si>
+    <t>ROLL  NO.</t>
+  </si>
+  <si>
+    <t>REG NO.</t>
+  </si>
+  <si>
+    <t>QUESTION NUMBER &gt;&gt;</t>
+  </si>
+  <si>
+    <t>PART A</t>
+  </si>
+  <si>
+    <t>Q. No.1</t>
+  </si>
+  <si>
+    <t>Q. No.2</t>
+  </si>
+  <si>
+    <t>Q. No.3</t>
+  </si>
+  <si>
+    <t>Q. No. 4</t>
+  </si>
+  <si>
+    <t>Q. No. 5</t>
+  </si>
+  <si>
+    <t>Q. No. 6</t>
+  </si>
+  <si>
+    <t>Q. No. 7</t>
+  </si>
+  <si>
+    <t>Q. No. 8</t>
+  </si>
+  <si>
+    <t>Q. No. 9</t>
+  </si>
+  <si>
+    <t>Q. No. 10</t>
+  </si>
+  <si>
+    <t>Q. No. 11</t>
+  </si>
+  <si>
+    <t>Q. No. 12</t>
+  </si>
+  <si>
+    <t>Q. No. 13</t>
+  </si>
+  <si>
+    <t>Q. No. 14</t>
+  </si>
+  <si>
+    <t>Q. No. 15</t>
+  </si>
+  <si>
+    <t>Q. No. 16</t>
+  </si>
+  <si>
+    <t>11.a</t>
+  </si>
+  <si>
+    <t>11.b</t>
+  </si>
+  <si>
+    <t>12.a</t>
+  </si>
+  <si>
+    <t>12.b</t>
+  </si>
+  <si>
+    <t>13.a</t>
+  </si>
+  <si>
+    <t>13.b</t>
+  </si>
+  <si>
+    <t>14.a</t>
+  </si>
+  <si>
+    <t>14.b</t>
+  </si>
+  <si>
+    <t>15 a</t>
+  </si>
+  <si>
+    <t>15 b</t>
+  </si>
+  <si>
+    <t>16.a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      16.b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                      MAXIMUM MARK &gt;&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                     </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>COURSE OUTCOME &gt;&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                        STUDENT NAME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,20 +174,58 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF9C0006"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -103,18 +234,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFB2A1C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -138,19 +335,108 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -161,18 +447,110 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -190,6 +568,146 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="COURSE ASSESSMENT"/>
+      <sheetName val="STUDENT NAMELIST"/>
+      <sheetName val="INTERNAL - I"/>
+      <sheetName val="INTERNAL - II "/>
+      <sheetName val="CO's Attainment"/>
+      <sheetName val="UNIT TEST"/>
+      <sheetName val="Assingment Attainment"/>
+      <sheetName val="Direct Attainment"/>
+      <sheetName val="UNIVERSITY EXAM"/>
+      <sheetName val="CO ATTAINMENT GAP"/>
+      <sheetName val="PO ATTAINMENT "/>
+      <sheetName val="New Internal - II"/>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="B2"/>
+          <cell r="C2"/>
+          <cell r="D2"/>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>REG.NO</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>ROLL.NO</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>STUDENT NAME</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4"/>
+          <cell r="C4"/>
+          <cell r="D4"/>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>2023PEC AI 541</v>
+          </cell>
+          <cell r="C5">
+            <v>211423243001</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>AATHISUDHAN A</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>2023PEC AI 542</v>
+          </cell>
+          <cell r="C6">
+            <v>211423243002</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>ABESHEK SRIRAMN</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>2023PEC AI 101</v>
+          </cell>
+          <cell r="C7">
+            <v>211423243003</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>ABINAYA M</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>2023PEC AI 543</v>
+          </cell>
+          <cell r="C8">
+            <v>211423243004</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>ABINESH KUMAR T</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>2023PEC AI 102</v>
+          </cell>
+          <cell r="C9">
+            <v>211423243005</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>ABIRAMI A</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>2023PEC AI 103</v>
+          </cell>
+          <cell r="C10">
+            <v>211423243006</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>ABIRAMI G</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>2023PEC AI 544</v>
+          </cell>
+          <cell r="C11">
+            <v>211423243007</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>ABISHAI SINGH J</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -489,63 +1007,1632 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F158DB7-B3F6-AB4B-B5E0-C4A2E84A7CDF}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="39.1640625" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="74.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+    </row>
+    <row r="2" spans="1:26" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="13"/>
+      <c r="U2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="14"/>
+      <c r="W2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z2" s="15"/>
+    </row>
+    <row r="3" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+    </row>
+    <row r="4" spans="1:26" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z4" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="22">
+        <v>2</v>
+      </c>
+      <c r="F5" s="22">
+        <v>2</v>
+      </c>
+      <c r="G5" s="22">
+        <v>2</v>
+      </c>
+      <c r="H5" s="22">
+        <v>2</v>
+      </c>
+      <c r="I5" s="22">
+        <v>2</v>
+      </c>
+      <c r="J5" s="22">
+        <v>2</v>
+      </c>
+      <c r="K5" s="22">
+        <v>2</v>
+      </c>
+      <c r="L5" s="22">
+        <v>2</v>
+      </c>
+      <c r="M5" s="22">
+        <v>2</v>
+      </c>
+      <c r="N5" s="22">
+        <v>2</v>
+      </c>
+      <c r="O5" s="22">
+        <v>13</v>
+      </c>
+      <c r="P5" s="22">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="22">
+        <v>13</v>
+      </c>
+      <c r="R5" s="22">
+        <v>13</v>
+      </c>
+      <c r="S5" s="22">
+        <v>13</v>
+      </c>
+      <c r="T5" s="22">
+        <v>13</v>
+      </c>
+      <c r="U5" s="22">
+        <v>13</v>
+      </c>
+      <c r="V5" s="22">
+        <v>13</v>
+      </c>
+      <c r="W5" s="22">
+        <v>13</v>
+      </c>
+      <c r="X5" s="22">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="22">
+        <v>15</v>
+      </c>
+      <c r="Z5" s="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+    </row>
+    <row r="7" spans="1:26" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+    </row>
+    <row r="8" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+    </row>
+    <row r="9" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="32">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B9" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C9" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D9" s="34" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="35">
+        <v>2</v>
+      </c>
+      <c r="F9" s="35">
+        <v>2</v>
+      </c>
+      <c r="G9" s="35">
+        <v>2</v>
+      </c>
+      <c r="H9" s="35">
+        <v>2</v>
+      </c>
+      <c r="I9" s="35">
+        <v>2</v>
+      </c>
+      <c r="J9" s="35">
+        <v>2</v>
+      </c>
+      <c r="K9" s="35">
+        <v>2</v>
+      </c>
+      <c r="L9" s="35">
+        <v>2</v>
+      </c>
+      <c r="M9" s="35">
+        <v>2</v>
+      </c>
+      <c r="N9" s="35">
+        <v>0</v>
+      </c>
+      <c r="O9" s="35">
+        <v>13</v>
+      </c>
+      <c r="P9" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="35">
+        <v>0</v>
+      </c>
+      <c r="R9" s="35">
+        <v>13</v>
+      </c>
+      <c r="S9" s="35">
+        <v>11</v>
+      </c>
+      <c r="T9" s="35">
+        <v>0</v>
+      </c>
+      <c r="U9" s="35">
+        <v>13</v>
+      </c>
+      <c r="V9" s="35">
+        <v>0</v>
+      </c>
+      <c r="W9" s="35">
+        <v>0</v>
+      </c>
+      <c r="X9" s="35">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="35">
+        <v>14</v>
+      </c>
+      <c r="Z9" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="32">
+        <v>2</v>
+      </c>
+      <c r="B10" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C10" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D10" s="34" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="35">
+        <v>2</v>
+      </c>
+      <c r="F10" s="35">
+        <v>2</v>
+      </c>
+      <c r="G10" s="35">
+        <v>2</v>
+      </c>
+      <c r="H10" s="35">
+        <v>2</v>
+      </c>
+      <c r="I10" s="35">
+        <v>2</v>
+      </c>
+      <c r="J10" s="35">
+        <v>2</v>
+      </c>
+      <c r="K10" s="35">
+        <v>2</v>
+      </c>
+      <c r="L10" s="35">
+        <v>0</v>
+      </c>
+      <c r="M10" s="35">
+        <v>0</v>
+      </c>
+      <c r="N10" s="35">
+        <v>0</v>
+      </c>
+      <c r="O10" s="35">
+        <v>0</v>
+      </c>
+      <c r="P10" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="35">
+        <v>10</v>
+      </c>
+      <c r="R10" s="35">
+        <v>0</v>
+      </c>
+      <c r="S10" s="35">
+        <v>0</v>
+      </c>
+      <c r="T10" s="35">
+        <v>10</v>
+      </c>
+      <c r="U10" s="35">
+        <v>0</v>
+      </c>
+      <c r="V10" s="35">
+        <v>10</v>
+      </c>
+      <c r="W10" s="35">
+        <v>5</v>
+      </c>
+      <c r="X10" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" s="32">
+        <v>3</v>
+      </c>
+      <c r="B11" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C11" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" s="34" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="35">
+        <v>2</v>
+      </c>
+      <c r="F11" s="35">
+        <v>2</v>
+      </c>
+      <c r="G11" s="35">
+        <v>2</v>
+      </c>
+      <c r="H11" s="35">
+        <v>2</v>
+      </c>
+      <c r="I11" s="35">
+        <v>2</v>
+      </c>
+      <c r="J11" s="35">
+        <v>2</v>
+      </c>
+      <c r="K11" s="35">
+        <v>2</v>
+      </c>
+      <c r="L11" s="35">
+        <v>2</v>
+      </c>
+      <c r="M11" s="35">
+        <v>1</v>
+      </c>
+      <c r="N11" s="35">
+        <v>0</v>
+      </c>
+      <c r="O11" s="35">
+        <v>12</v>
+      </c>
+      <c r="P11" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="35">
+        <v>0</v>
+      </c>
+      <c r="R11" s="35">
+        <v>12</v>
+      </c>
+      <c r="S11" s="35">
+        <v>11</v>
+      </c>
+      <c r="T11" s="35">
+        <v>0</v>
+      </c>
+      <c r="U11" s="35">
+        <v>12</v>
+      </c>
+      <c r="V11" s="35">
+        <v>0</v>
+      </c>
+      <c r="W11" s="35">
+        <v>0</v>
+      </c>
+      <c r="X11" s="35">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="35">
+        <v>13</v>
+      </c>
+      <c r="Z11" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A12" s="32">
+        <v>4</v>
+      </c>
+      <c r="B12" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C12" s="33" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D12" s="34" t="e">
+        <f>'[1]STUDENT NAMELIST'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="35">
+        <v>2</v>
+      </c>
+      <c r="F12" s="35">
+        <v>2</v>
+      </c>
+      <c r="G12" s="35">
+        <v>2</v>
+      </c>
+      <c r="H12" s="35">
+        <v>2</v>
+      </c>
+      <c r="I12" s="35">
+        <v>2</v>
+      </c>
+      <c r="J12" s="35">
+        <v>2</v>
+      </c>
+      <c r="K12" s="35">
+        <v>0</v>
+      </c>
+      <c r="L12" s="35">
+        <v>0</v>
+      </c>
+      <c r="M12" s="35">
+        <v>0</v>
+      </c>
+      <c r="N12" s="35">
+        <v>0</v>
+      </c>
+      <c r="O12" s="35">
+        <v>0</v>
+      </c>
+      <c r="P12" s="35">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="35">
         <v>9</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="R12" s="35">
+        <v>0</v>
+      </c>
+      <c r="S12" s="35">
+        <v>0</v>
+      </c>
+      <c r="T12" s="35">
+        <v>9</v>
+      </c>
+      <c r="U12" s="35">
+        <v>0</v>
+      </c>
+      <c r="V12" s="35">
+        <v>9</v>
+      </c>
+      <c r="W12" s="35">
+        <v>4</v>
+      </c>
+      <c r="X12" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="35">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="4" t="s">
+    <row r="13" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A13" s="32">
+        <v>5</v>
+      </c>
+      <c r="B13" s="33">
+        <f>'[1]STUDENT NAMELIST'!B1</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="33">
+        <f>'[1]STUDENT NAMELIST'!C1</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
+        <f>'[1]STUDENT NAMELIST'!D1</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="35">
+        <v>2</v>
+      </c>
+      <c r="F13" s="35">
+        <v>2</v>
+      </c>
+      <c r="G13" s="35">
+        <v>2</v>
+      </c>
+      <c r="H13" s="35">
+        <v>2</v>
+      </c>
+      <c r="I13" s="35">
+        <v>2</v>
+      </c>
+      <c r="J13" s="35">
+        <v>2</v>
+      </c>
+      <c r="K13" s="35">
+        <v>2</v>
+      </c>
+      <c r="L13" s="35">
+        <v>2</v>
+      </c>
+      <c r="M13" s="35">
+        <v>2</v>
+      </c>
+      <c r="N13" s="35">
+        <v>1</v>
+      </c>
+      <c r="O13" s="35">
+        <v>13</v>
+      </c>
+      <c r="P13" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="35">
+        <v>0</v>
+      </c>
+      <c r="R13" s="35">
+        <v>13</v>
+      </c>
+      <c r="S13" s="35">
+        <v>12</v>
+      </c>
+      <c r="T13" s="35">
+        <v>0</v>
+      </c>
+      <c r="U13" s="35">
+        <v>13</v>
+      </c>
+      <c r="V13" s="35">
+        <v>0</v>
+      </c>
+      <c r="W13" s="35">
+        <v>0</v>
+      </c>
+      <c r="X13" s="35">
+        <v>11</v>
+      </c>
+      <c r="Y13" s="35">
+        <v>14</v>
+      </c>
+      <c r="Z13" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A14" s="32">
+        <v>6</v>
+      </c>
+      <c r="B14" s="33">
+        <f>'[1]STUDENT NAMELIST'!B2</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="33">
+        <f>'[1]STUDENT NAMELIST'!C2</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
+        <f>'[1]STUDENT NAMELIST'!D2</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="35">
+        <v>2</v>
+      </c>
+      <c r="F14" s="35">
+        <v>2</v>
+      </c>
+      <c r="G14" s="35">
+        <v>2</v>
+      </c>
+      <c r="H14" s="35">
+        <v>2</v>
+      </c>
+      <c r="I14" s="35">
+        <v>2</v>
+      </c>
+      <c r="J14" s="35">
+        <v>2</v>
+      </c>
+      <c r="K14" s="35">
+        <v>0</v>
+      </c>
+      <c r="L14" s="35">
+        <v>0</v>
+      </c>
+      <c r="M14" s="35">
+        <v>0</v>
+      </c>
+      <c r="N14" s="35">
+        <v>0</v>
+      </c>
+      <c r="O14" s="35">
+        <v>0</v>
+      </c>
+      <c r="P14" s="35">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="35">
+        <v>9</v>
+      </c>
+      <c r="R14" s="35">
+        <v>0</v>
+      </c>
+      <c r="S14" s="35">
+        <v>0</v>
+      </c>
+      <c r="T14" s="35">
+        <v>9</v>
+      </c>
+      <c r="U14" s="35">
+        <v>0</v>
+      </c>
+      <c r="V14" s="35">
+        <v>9</v>
+      </c>
+      <c r="W14" s="35">
+        <v>5</v>
+      </c>
+      <c r="X14" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="32">
+        <v>7</v>
+      </c>
+      <c r="B15" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B3</f>
+        <v>REG.NO</v>
+      </c>
+      <c r="C15" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!C3</f>
+        <v>ROLL.NO</v>
+      </c>
+      <c r="D15" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D3</f>
+        <v>STUDENT NAME</v>
+      </c>
+      <c r="E15" s="35">
+        <v>2</v>
+      </c>
+      <c r="F15" s="35">
+        <v>2</v>
+      </c>
+      <c r="G15" s="35">
+        <v>2</v>
+      </c>
+      <c r="H15" s="35">
+        <v>2</v>
+      </c>
+      <c r="I15" s="35">
+        <v>2</v>
+      </c>
+      <c r="J15" s="35">
+        <v>1</v>
+      </c>
+      <c r="K15" s="35">
+        <v>0</v>
+      </c>
+      <c r="L15" s="35">
+        <v>0</v>
+      </c>
+      <c r="M15" s="35">
+        <v>0</v>
+      </c>
+      <c r="N15" s="35">
+        <v>0</v>
+      </c>
+      <c r="O15" s="35">
+        <v>8</v>
+      </c>
+      <c r="P15" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="35">
+        <v>0</v>
+      </c>
+      <c r="R15" s="35">
+        <v>8</v>
+      </c>
+      <c r="S15" s="35">
+        <v>7</v>
+      </c>
+      <c r="T15" s="35">
+        <v>0</v>
+      </c>
+      <c r="U15" s="35">
+        <v>8</v>
+      </c>
+      <c r="V15" s="35">
+        <v>0</v>
+      </c>
+      <c r="W15" s="35">
+        <v>0</v>
+      </c>
+      <c r="X15" s="35">
+        <v>6</v>
+      </c>
+      <c r="Y15" s="35">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A16" s="32">
+        <v>8</v>
+      </c>
+      <c r="B16" s="33">
+        <f>'[1]STUDENT NAMELIST'!B4</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="33">
+        <f>'[1]STUDENT NAMELIST'!C4</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
+        <f>'[1]STUDENT NAMELIST'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="35">
+        <v>2</v>
+      </c>
+      <c r="F16" s="35">
+        <v>2</v>
+      </c>
+      <c r="G16" s="35">
+        <v>2</v>
+      </c>
+      <c r="H16" s="35">
+        <v>0</v>
+      </c>
+      <c r="I16" s="35">
+        <v>0</v>
+      </c>
+      <c r="J16" s="35">
+        <v>0</v>
+      </c>
+      <c r="K16" s="35">
+        <v>0</v>
+      </c>
+      <c r="L16" s="35">
+        <v>0</v>
+      </c>
+      <c r="M16" s="35">
+        <v>0</v>
+      </c>
+      <c r="N16" s="35">
+        <v>0</v>
+      </c>
+      <c r="O16" s="35">
+        <v>0</v>
+      </c>
+      <c r="P16" s="35">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="Q16" s="35">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="R16" s="35">
+        <v>0</v>
+      </c>
+      <c r="S16" s="35">
+        <v>0</v>
+      </c>
+      <c r="T16" s="35">
+        <v>5</v>
+      </c>
+      <c r="U16" s="35">
+        <v>0</v>
+      </c>
+      <c r="V16" s="35">
+        <v>5</v>
+      </c>
+      <c r="W16" s="35">
+        <v>0</v>
+      </c>
+      <c r="X16" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="32">
+        <v>9</v>
+      </c>
+      <c r="B17" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B5</f>
+        <v>2023PEC AI 541</v>
+      </c>
+      <c r="C17" s="33">
+        <f>'[1]STUDENT NAMELIST'!C5</f>
+        <v>211423243001</v>
+      </c>
+      <c r="D17" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D5</f>
+        <v>AATHISUDHAN A</v>
+      </c>
+      <c r="E17" s="35">
+        <v>2</v>
+      </c>
+      <c r="F17" s="35">
+        <v>2</v>
+      </c>
+      <c r="G17" s="35">
+        <v>2</v>
+      </c>
+      <c r="H17" s="35">
+        <v>2</v>
+      </c>
+      <c r="I17" s="35">
+        <v>2</v>
+      </c>
+      <c r="J17" s="35">
+        <v>2</v>
+      </c>
+      <c r="K17" s="35">
+        <v>2</v>
+      </c>
+      <c r="L17" s="35">
+        <v>2</v>
+      </c>
+      <c r="M17" s="35">
+        <v>2</v>
+      </c>
+      <c r="N17" s="35">
+        <v>1</v>
+      </c>
+      <c r="O17" s="35">
+        <v>13</v>
+      </c>
+      <c r="P17" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="35">
+        <v>0</v>
+      </c>
+      <c r="R17" s="35">
+        <v>13</v>
+      </c>
+      <c r="S17" s="35">
+        <v>12</v>
+      </c>
+      <c r="T17" s="35">
+        <v>0</v>
+      </c>
+      <c r="U17" s="35">
+        <v>13</v>
+      </c>
+      <c r="V17" s="35">
+        <v>0</v>
+      </c>
+      <c r="W17" s="35">
+        <v>0</v>
+      </c>
+      <c r="X17" s="35">
+        <v>9</v>
+      </c>
+      <c r="Y17" s="35">
+        <v>14</v>
+      </c>
+      <c r="Z17" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="32">
+        <v>10</v>
+      </c>
+      <c r="B18" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B6</f>
+        <v>2023PEC AI 542</v>
+      </c>
+      <c r="C18" s="33">
+        <f>'[1]STUDENT NAMELIST'!C6</f>
+        <v>211423243002</v>
+      </c>
+      <c r="D18" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D6</f>
+        <v>ABESHEK SRIRAMN</v>
+      </c>
+      <c r="E18" s="35">
+        <v>2</v>
+      </c>
+      <c r="F18" s="35">
+        <v>2</v>
+      </c>
+      <c r="G18" s="35">
+        <v>2</v>
+      </c>
+      <c r="H18" s="35">
+        <v>2</v>
+      </c>
+      <c r="I18" s="35">
+        <v>2</v>
+      </c>
+      <c r="J18" s="35">
+        <v>0</v>
+      </c>
+      <c r="K18" s="35">
+        <v>0</v>
+      </c>
+      <c r="L18" s="35">
+        <v>0</v>
+      </c>
+      <c r="M18" s="35">
+        <v>0</v>
+      </c>
+      <c r="N18" s="35">
+        <v>0</v>
+      </c>
+      <c r="O18" s="35">
+        <v>0</v>
+      </c>
+      <c r="P18" s="35">
         <v>7</v>
+      </c>
+      <c r="Q18" s="35">
+        <v>7</v>
+      </c>
+      <c r="R18" s="35">
+        <v>0</v>
+      </c>
+      <c r="S18" s="35">
+        <v>0</v>
+      </c>
+      <c r="T18" s="35">
+        <v>7</v>
+      </c>
+      <c r="U18" s="35">
+        <v>0</v>
+      </c>
+      <c r="V18" s="35">
+        <v>7</v>
+      </c>
+      <c r="W18" s="35">
+        <v>4</v>
+      </c>
+      <c r="X18" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="32">
+        <v>11</v>
+      </c>
+      <c r="B19" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B7</f>
+        <v>2023PEC AI 101</v>
+      </c>
+      <c r="C19" s="33">
+        <f>'[1]STUDENT NAMELIST'!C7</f>
+        <v>211423243003</v>
+      </c>
+      <c r="D19" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D7</f>
+        <v>ABINAYA M</v>
+      </c>
+      <c r="E19" s="35">
+        <v>2</v>
+      </c>
+      <c r="F19" s="35">
+        <v>2</v>
+      </c>
+      <c r="G19" s="35">
+        <v>2</v>
+      </c>
+      <c r="H19" s="35">
+        <v>2</v>
+      </c>
+      <c r="I19" s="35">
+        <v>2</v>
+      </c>
+      <c r="J19" s="35">
+        <v>2</v>
+      </c>
+      <c r="K19" s="35">
+        <v>2</v>
+      </c>
+      <c r="L19" s="35">
+        <v>1</v>
+      </c>
+      <c r="M19" s="35">
+        <v>0</v>
+      </c>
+      <c r="N19" s="35">
+        <v>0</v>
+      </c>
+      <c r="O19" s="35">
+        <v>11</v>
+      </c>
+      <c r="P19" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="35">
+        <v>0</v>
+      </c>
+      <c r="R19" s="35">
+        <v>11</v>
+      </c>
+      <c r="S19" s="35">
+        <v>9</v>
+      </c>
+      <c r="T19" s="35">
+        <v>0</v>
+      </c>
+      <c r="U19" s="35">
+        <v>11</v>
+      </c>
+      <c r="V19" s="35">
+        <v>0</v>
+      </c>
+      <c r="W19" s="35">
+        <v>0</v>
+      </c>
+      <c r="X19" s="35">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="35">
+        <v>11</v>
+      </c>
+      <c r="Z19" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A20" s="32">
+        <v>12</v>
+      </c>
+      <c r="B20" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B8</f>
+        <v>2023PEC AI 543</v>
+      </c>
+      <c r="C20" s="33">
+        <f>'[1]STUDENT NAMELIST'!C8</f>
+        <v>211423243004</v>
+      </c>
+      <c r="D20" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D8</f>
+        <v>ABINESH KUMAR T</v>
+      </c>
+      <c r="E20" s="35">
+        <v>2</v>
+      </c>
+      <c r="F20" s="35">
+        <v>2</v>
+      </c>
+      <c r="G20" s="35">
+        <v>2</v>
+      </c>
+      <c r="H20" s="35">
+        <v>0</v>
+      </c>
+      <c r="I20" s="35">
+        <v>0</v>
+      </c>
+      <c r="J20" s="35">
+        <v>0</v>
+      </c>
+      <c r="K20" s="35">
+        <v>0</v>
+      </c>
+      <c r="L20" s="35">
+        <v>0</v>
+      </c>
+      <c r="M20" s="35">
+        <v>0</v>
+      </c>
+      <c r="N20" s="35">
+        <v>0</v>
+      </c>
+      <c r="O20" s="35">
+        <v>0</v>
+      </c>
+      <c r="P20" s="35">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="35">
+        <v>5</v>
+      </c>
+      <c r="R20" s="35">
+        <v>0</v>
+      </c>
+      <c r="S20" s="35">
+        <v>0</v>
+      </c>
+      <c r="T20" s="35">
+        <v>5</v>
+      </c>
+      <c r="U20" s="35">
+        <v>0</v>
+      </c>
+      <c r="V20" s="35">
+        <v>5</v>
+      </c>
+      <c r="W20" s="35">
+        <v>0</v>
+      </c>
+      <c r="X20" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A21" s="32">
+        <v>13</v>
+      </c>
+      <c r="B21" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B9</f>
+        <v>2023PEC AI 102</v>
+      </c>
+      <c r="C21" s="33">
+        <f>'[1]STUDENT NAMELIST'!C9</f>
+        <v>211423243005</v>
+      </c>
+      <c r="D21" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D9</f>
+        <v>ABIRAMI A</v>
+      </c>
+      <c r="E21" s="35">
+        <v>2</v>
+      </c>
+      <c r="F21" s="35">
+        <v>2</v>
+      </c>
+      <c r="G21" s="35">
+        <v>2</v>
+      </c>
+      <c r="H21" s="35">
+        <v>2</v>
+      </c>
+      <c r="I21" s="35">
+        <v>2</v>
+      </c>
+      <c r="J21" s="35">
+        <v>0</v>
+      </c>
+      <c r="K21" s="35">
+        <v>0</v>
+      </c>
+      <c r="L21" s="35">
+        <v>0</v>
+      </c>
+      <c r="M21" s="35">
+        <v>0</v>
+      </c>
+      <c r="N21" s="35">
+        <v>0</v>
+      </c>
+      <c r="O21" s="35">
+        <v>8</v>
+      </c>
+      <c r="P21" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="35">
+        <v>0</v>
+      </c>
+      <c r="R21" s="35">
+        <v>8</v>
+      </c>
+      <c r="S21" s="35">
+        <v>7</v>
+      </c>
+      <c r="T21" s="35">
+        <v>0</v>
+      </c>
+      <c r="U21" s="35">
+        <v>8</v>
+      </c>
+      <c r="V21" s="35">
+        <v>0</v>
+      </c>
+      <c r="W21" s="35">
+        <v>0</v>
+      </c>
+      <c r="X21" s="35">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="35">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A22" s="32">
+        <v>14</v>
+      </c>
+      <c r="B22" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B10</f>
+        <v>2023PEC AI 103</v>
+      </c>
+      <c r="C22" s="33">
+        <f>'[1]STUDENT NAMELIST'!C10</f>
+        <v>211423243006</v>
+      </c>
+      <c r="D22" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D10</f>
+        <v>ABIRAMI G</v>
+      </c>
+      <c r="E22" s="36">
+        <v>2</v>
+      </c>
+      <c r="F22" s="36">
+        <v>2</v>
+      </c>
+      <c r="G22" s="36">
+        <v>2</v>
+      </c>
+      <c r="H22" s="36">
+        <v>2</v>
+      </c>
+      <c r="I22" s="36">
+        <v>2</v>
+      </c>
+      <c r="J22" s="36">
+        <v>2</v>
+      </c>
+      <c r="K22" s="36">
+        <v>2</v>
+      </c>
+      <c r="L22" s="36">
+        <v>2</v>
+      </c>
+      <c r="M22" s="36">
+        <v>2</v>
+      </c>
+      <c r="N22" s="36">
+        <v>1</v>
+      </c>
+      <c r="O22" s="36">
+        <v>0</v>
+      </c>
+      <c r="P22" s="35">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="35">
+        <v>13</v>
+      </c>
+      <c r="R22" s="35">
+        <v>0</v>
+      </c>
+      <c r="S22" s="35">
+        <v>0</v>
+      </c>
+      <c r="T22" s="35">
+        <v>13</v>
+      </c>
+      <c r="U22" s="35">
+        <v>0</v>
+      </c>
+      <c r="V22" s="35">
+        <v>13</v>
+      </c>
+      <c r="W22" s="35">
+        <v>8</v>
+      </c>
+      <c r="X22" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="35">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="18" x14ac:dyDescent="0.2">
+      <c r="A23" s="32">
+        <v>15</v>
+      </c>
+      <c r="B23" s="33" t="str">
+        <f>'[1]STUDENT NAMELIST'!B11</f>
+        <v>2023PEC AI 544</v>
+      </c>
+      <c r="C23" s="33">
+        <f>'[1]STUDENT NAMELIST'!C11</f>
+        <v>211423243007</v>
+      </c>
+      <c r="D23" s="34" t="str">
+        <f>'[1]STUDENT NAMELIST'!D11</f>
+        <v>ABISHAI SINGH J</v>
+      </c>
+      <c r="E23" s="36">
+        <v>2</v>
+      </c>
+      <c r="F23" s="36">
+        <v>2</v>
+      </c>
+      <c r="G23" s="36">
+        <v>2</v>
+      </c>
+      <c r="H23" s="36">
+        <v>0</v>
+      </c>
+      <c r="I23" s="36">
+        <v>0</v>
+      </c>
+      <c r="J23" s="36">
+        <v>0</v>
+      </c>
+      <c r="K23" s="36">
+        <v>0</v>
+      </c>
+      <c r="L23" s="36">
+        <v>0</v>
+      </c>
+      <c r="M23" s="36">
+        <v>0</v>
+      </c>
+      <c r="N23" s="36">
+        <v>0</v>
+      </c>
+      <c r="O23" s="36">
+        <v>5</v>
+      </c>
+      <c r="P23" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="35">
+        <v>0</v>
+      </c>
+      <c r="R23" s="35">
+        <v>5</v>
+      </c>
+      <c r="S23" s="35">
+        <v>4</v>
+      </c>
+      <c r="T23" s="35">
+        <v>0</v>
+      </c>
+      <c r="U23" s="35">
+        <v>5</v>
+      </c>
+      <c r="V23" s="35">
+        <v>0</v>
+      </c>
+      <c r="W23" s="35">
+        <v>0</v>
+      </c>
+      <c r="X23" s="35">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="35">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="35">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
+  <mergeCells count="24">
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="Y2:Z3"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="O1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="Q2:R3"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="B1:B8"/>
+    <mergeCell ref="C1:C8"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:N1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="ERROR - Enter only valid CO's or NA" sqref="E6:N6" xr:uid="{C57B3BD9-6EE0-4D4D-8317-568E3C88C1B6}">
+      <formula1>$F$11:$L$11</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>